--- a/Data/Quantifications/B04_B_To_C01_Z20_01.xlsx
+++ b/Data/Quantifications/B04_B_To_C01_Z20_01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dagos\Desktop\PhD_local\Experience1\Codes\Data\Quantifications\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdagostino\Desktop\GITHUB\TRoot\Data\Quantifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40263A4E-25C3-4955-8E5C-DA09427FA314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACEFD30-5B88-4C85-A92E-2FAA0D62C0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{B1674AB4-2BF8-40B9-8D66-EEE3CC00AB7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="10" xr2:uid="{B1674AB4-2BF8-40B9-8D66-EEE3CC00AB7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Xylem" sheetId="1" r:id="rId1"/>
@@ -157,9 +157,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -197,7 +197,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -303,7 +303,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -445,7 +445,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -454,7 +454,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5940B283-4889-4BDF-89E4-7A3EC993BCA4}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -562,7 +562,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{919A08D0-CACC-4185-8D34-6DF5F0D524FC}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
     <col min="3" max="3" width="18.28515625" customWidth="1"/>
@@ -609,7 +609,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{343D18CA-D4FA-4113-9DA4-FF3B2057B8DB}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -731,7 +731,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F4BE9EF-D018-4AFE-9538-CFC900B118B4}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -923,7 +923,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7566D056-5448-44BF-86D9-9F4701B9C010}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -967,7 +967,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ACF9A60-CC0F-489F-A382-38A11877EA05}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="11.5703125" customWidth="1"/>
   </cols>
@@ -1184,7 +1184,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C271ED1B-9971-41F3-B5A0-395862FF5C96}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1381,7 +1381,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88FE87F7-E3DB-4D26-8101-4C3BDE61B328}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1510,7 +1510,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8953B999-1DEC-489B-A076-7D52C6B6F454}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1673,7 +1673,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E216AEB7-2346-4EB0-9A67-7096DABD24F2}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1768,7 +1768,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18D270DC-9578-44D5-95CA-1E01C0BBC52C}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
